--- a/Result/profitability/6184.xlsx
+++ b/Result/profitability/6184.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>0.84</v>
       </c>
       <c r="M2" t="n">
-        <v>0.75625</v>
+        <v>0.725</v>
       </c>
       <c r="N2" t="n">
-        <v>53.28125</v>
+        <v>52.8175</v>
       </c>
       <c r="O2" t="n">
         <v>1</v>
@@ -780,10 +780,10 @@
         <v>0.33</v>
       </c>
       <c r="M3" t="n">
-        <v>0.6675</v>
+        <v>0.6587499999999999</v>
       </c>
       <c r="N3" t="n">
-        <v>52.705</v>
+        <v>52.96625</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>0.76</v>
       </c>
       <c r="M4" t="n">
-        <v>0.655</v>
+        <v>0.6412500000000001</v>
       </c>
       <c r="N4" t="n">
-        <v>53.26625</v>
+        <v>53.41625000000001</v>
       </c>
       <c r="O4" t="n">
         <v>1</v>
@@ -1018,10 +1018,10 @@
         <v>1.16</v>
       </c>
       <c r="M5" t="n">
-        <v>0.6875</v>
+        <v>0.6775</v>
       </c>
       <c r="N5" t="n">
-        <v>54.1575</v>
+        <v>54.175</v>
       </c>
       <c r="O5" t="n">
         <v>1</v>
@@ -1137,10 +1137,10 @@
         <v>1.08</v>
       </c>
       <c r="M6" t="n">
-        <v>0.71375</v>
+        <v>0.7112499999999999</v>
       </c>
       <c r="N6" t="n">
-        <v>54.755</v>
+        <v>54.85875</v>
       </c>
       <c r="O6" t="n">
         <v>1</v>
@@ -1264,10 +1264,10 @@
         <v>1.11</v>
       </c>
       <c r="M7" t="n">
-        <v>0.75125</v>
+        <v>0.8475</v>
       </c>
       <c r="N7" t="n">
-        <v>55.5075</v>
+        <v>55.67875</v>
       </c>
       <c r="O7" t="n">
         <v>1</v>
@@ -1391,10 +1391,10 @@
         <v>1.07</v>
       </c>
       <c r="M8" t="n">
-        <v>0.8825000000000001</v>
+        <v>0.8925000000000001</v>
       </c>
       <c r="N8" t="n">
-        <v>56.14875</v>
+        <v>56.0625</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -9826,6 +9826,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>6184</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>546</v>
+      </c>
+      <c r="D75" t="n">
+        <v>254</v>
+      </c>
+      <c r="E75" t="n">
+        <v>292</v>
+      </c>
+      <c r="F75" t="n">
+        <v>53.53</v>
+      </c>
+      <c r="G75" t="n">
+        <v>154</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>28.26%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>30</v>
+      </c>
+      <c r="J75" t="n">
+        <v>184</v>
+      </c>
+      <c r="K75" t="n">
+        <v>121</v>
+      </c>
+      <c r="L75" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="M75" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="N75" t="n">
+        <v>53.37625</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>1</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>0.08000000000000007</v>
+      </c>
+      <c r="X75" t="n">
+        <v>0.1126760563380282</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>-0.6899999999999977</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>-0.01272593139063072</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>-0.07999999999999996</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>-0.09195402298850575</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>0.1400000000000006</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>0.00262221389773365</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS衰退 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
